--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -262,13 +262,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -905,7 +905,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15587,7 +15587,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16083,7 +16083,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16269,7 +16269,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16889,7 +16889,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17137,7 +17137,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17571,7 +17571,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17757,7 +17757,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18005,7 +18005,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18067,7 +18067,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18253,7 +18253,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18377,7 +18377,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18687,7 +18687,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18935,7 +18935,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19369,7 +19369,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19617,7 +19617,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20361,7 +20361,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21787,7 +21787,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21849,7 +21849,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22097,7 +22097,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22159,7 +22159,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22345,7 +22345,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22469,7 +22469,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22593,7 +22593,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22841,7 +22841,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22903,7 +22903,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23089,7 +23089,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23275,7 +23275,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23399,7 +23399,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23647,7 +23647,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23957,7 +23957,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24081,7 +24081,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24329,7 +24329,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24453,7 +24453,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24515,7 +24515,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24577,7 +24577,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24639,7 +24639,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24763,7 +24763,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24887,7 +24887,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25135,7 +25135,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25259,7 +25259,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25321,7 +25321,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25383,7 +25383,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25507,7 +25507,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25755,7 +25755,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25817,7 +25817,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25879,7 +25879,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -26003,7 +26003,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -26065,7 +26065,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26189,7 +26189,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26375,7 +26375,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26437,7 +26437,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26499,7 +26499,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26685,7 +26685,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26871,7 +26871,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26933,7 +26933,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26995,7 +26995,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -27057,7 +27057,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27119,7 +27119,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27181,7 +27181,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27243,7 +27243,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27367,7 +27367,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27553,7 +27553,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27863,7 +27863,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27987,7 +27987,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -28049,7 +28049,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28111,7 +28111,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28173,7 +28173,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28235,7 +28235,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28297,7 +28297,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28359,7 +28359,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28545,7 +28545,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28720,10 +28720,31 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 -
@@ -28731,7 +28752,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1034呎 (3房)
 -
@@ -28739,17 +28760,17 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 1083呎 (3房)
 $3890万
 $35,921/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr">
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>P2 | 3120呎 (4+房)
 -
@@ -28757,19 +28778,40 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1593万
+$32,776/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1142万
+$23,109/呎
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1235万
+$23,892/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28777,41 +28819,48 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
-$1593万
-$32,776/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
+$1566万
+$32,222/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
-$1142万
-$23,109/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
+$1130万
+$22,881/呎
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
-$1235万
-$23,892/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+$1276万
+$24,689/呎
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28819,64 +28868,15 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1566万
-$32,222/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1130万
-$22,881/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1276万
-$24,689/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $10775万
 $63,158/呎
-(26年-01月-26日)</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr"/>
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -28884,48 +28884,48 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1429万
 $29,401/呎
-(26年-03月-05日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
+(26年-03月-06日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1227万
 $24,844/呎
-(25年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
+(25年-08月-11日)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1245万
 $24,087/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $7296万
 $47,500/呎
-(25年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
+(25年-11月-06日)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8530万
 $50,000/呎
-(25年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr"/>
+(25年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -28933,48 +28933,48 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1117万
 $22,990/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1131万
 $22,903/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1154万
 $22,317/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr"/>
-      <c r="F10" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6543万
 $42,600/呎
-(25年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
+(25年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8189万
 $48,000/呎
-(25年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr"/>
+(25年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -28982,48 +28982,48 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1086万
 $22,346/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1100万
 $22,265/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1217万
 $23,536/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr"/>
-      <c r="F11" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6420万
 $41,800/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7558万
 $44,300/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr"/>
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -29031,48 +29031,48 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
 $22,292/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1097万
 $22,211/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1137万
 $21,986/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr"/>
-      <c r="F12" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6298万
 $41,000/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7421万
 $43,500/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr"/>
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -29080,48 +29080,48 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1067万
 $21,963/呎
-(25年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
+(25年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1081万
 $21,881/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1128万
 $21,822/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr"/>
-      <c r="F13" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6089万
 $39,641/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7319万
 $42,900/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr"/>
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -29129,48 +29129,48 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1048万
 $21,562/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1061万
 $21,482/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1123万
 $21,714/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr"/>
-      <c r="F14" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5990万
 $39,000/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6726万
 $39,425/呎
-(25年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr"/>
+(25年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -29178,48 +29178,48 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1107万
 $22,772/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1055万
 $21,354/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1187万
 $22,956/呎
-(25年-06月-19日)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr"/>
-      <c r="F15" s="21" t="inlineStr">
+(25年-06月-20日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5574万
 $36,290/呎
-(25年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
+(25年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6596万
 $38,665/呎
-(25年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr"/>
+(25年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -29227,48 +29227,48 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1100万
 $22,638/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1114万
 $22,553/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1112万
 $21,499/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr"/>
-      <c r="F16" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5076万
 $33,047/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6467万
 $37,906/呎
-(25年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr"/>
+(25年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -29276,48 +29276,48 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1094万
 $22,502/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1108万
 $22,419/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1175万
 $22,729/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr"/>
-      <c r="F17" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1469呎 (4+房)
 $5739万
 $39,066/呎
-(25年-06月-18日)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
+(25年-06月-19日)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6739万
 $39,501/呎
-(25年-06月-18日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr"/>
+(25年-06月-19日)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -29325,60 +29325,60 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1025万
 $21,095/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1036万
 $20,972/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1084万
 $20,973/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1011万
 $21,201/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>P1 | 1258呎 (4+房)
 $4422万
 $35,149/呎
-(25年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+(25年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2694万
 $30,970/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3313万
 $34,800/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -29388,60 +29388,60 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1021万
 $21,010/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1032万
 $20,889/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1066万
 $20,629/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1005万
 $21,073/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4351万
 $34,508/呎
-(25年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+(25年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2653万
 $30,495/呎
-(25年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
+(25年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3447万
 $36,211/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -29451,60 +29451,60 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1017万
 $20,926/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1028万
 $20,806/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1076万
 $20,805/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $999万
 $20,948/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4540万
 $36,000/呎
-(25年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+(25年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2612万
 $30,020/呎
-(25年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
+(25年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3256万
 $34,200/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -29514,60 +29514,60 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1013万
 $20,844/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1024万
 $20,723/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1138万
 $22,017/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $993万
 $20,824/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4265万
 $33,820/呎
-(25年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+(25年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2579万
 $29,640/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3220万
 $33,820/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -29577,60 +29577,60 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1009万
 $20,759/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1020万
 $20,640/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1067万
 $20,640/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $987万
 $20,700/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4229万
 $33,535/呎
-(25年-06月-19日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+(25年-06月-20日)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2688万
 $30,900/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3056万
 $32,100/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -29640,60 +29640,60 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1005万
 $20,677/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1079万
 $21,842/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1063万
 $20,557/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $984万
 $20,618/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4193万
 $33,250/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2529万
 $29,070/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2876万
 $30,210/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -29703,60 +29703,60 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1001万
 $20,595/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1008万
 $20,397/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1059万
 $20,476/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $980万
 $20,537/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4184万
 $33,180/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2504万
 $28,785/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3299万
 $34,651/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -29766,60 +29766,60 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $997万
 $20,512/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1004万
 $20,316/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1113万
 $21,522/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1037万
 $21,732/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4374万
 $34,688/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2480万
 $28,500/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3122万
 $32,791/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -29829,60 +29829,60 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $993万
 $20,430/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1000万
 $20,235/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1043万
 $20,176/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $972万
 $20,371/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3725万
 $29,538/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2406万
 $27,653/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2893万
 $30,386/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -29892,60 +29892,60 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $989万
 $20,350/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $996万
 $20,154/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1039万
 $20,095/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $968万
 $20,291/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3680万
 $29,187/呎
-(25年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
+(25年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2526万
 $29,032/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2850万
 $29,936/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -29955,60 +29955,60 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $985万
 $20,270/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $992万
 $20,073/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1022万
 $19,764/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1024万
 $21,474/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3955万
 $31,363/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2349万
 $27,001/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2652万
 $27,852/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -30018,60 +30018,60 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $981万
 $20,189/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1049万
 $21,243/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1095万
 $21,182/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
 $19,878/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3818万
 $30,281/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2319万
 $26,654/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2784万
 $29,242/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -30081,60 +30081,60 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1038万
 $21,364/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1045万
 $21,158/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1091万
 $21,097/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
 $20,050/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3862万
 $30,626/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2396万
 $27,545/呎
-(25年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
+(25年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2708万
 $28,441/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -30144,60 +30144,60 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
 $21,278/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1041万
 $21,073/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1086万
 $21,012/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $952万
 $19,969/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3819万
 $30,289/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2361万
 $27,138/呎
-(25年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
+(25年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2668万
 $28,021/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -30207,60 +30207,60 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1030万
 $21,195/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $976万
 $19,755/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1006万
 $19,451/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $949万
 $19,891/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3785万
 $30,014/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2338万
 $26,869/呎
-(25年-09月-17日)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
+(25年-09月-18日)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2641万
 $27,744/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -30270,60 +30270,60 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1026万
 $21,109/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1033万
 $20,907/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1014万
 $19,619/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $945万
 $19,811/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3474万
 $27,550/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2306万
 $26,506/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="H33" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2578万
 $27,075/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -30333,60 +30333,60 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $962万
 $19,788/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $968万
 $19,597/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1010万
 $19,542/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
 $19,654/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3632万
 $28,800/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2392万
 $27,500/呎
-(25年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
+(25年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2586万
 $27,168/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -30396,60 +30396,60 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1018万
 $20,940/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $964万
 $19,520/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1069万
 $20,681/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
 $19,459/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3426万
 $27,170/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2399万
 $27,579/呎
-(25年-08月-25日)</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
+(25年-08月-26日)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2675万
 $28,100/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -30459,60 +30459,60 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1014万
 $20,858/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $960万
 $19,441/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1002万
 $19,387/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $976万
 $20,470/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3881万
 $30,779/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2314万
 $26,600/呎
-(25年-09月-08日)</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
+(25年-09月-09日)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2570万
 $27,000/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -30522,60 +30522,60 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1010万
 $20,776/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $957万
 $19,364/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $998万
 $19,309/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $910万
 $19,075/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3577万
 $28,368/呎
-(25年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
+(25年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2490万
 $28,620/呎
-(25年-12月-30日)</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
+(25年-12月-31日)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2686万
 $28,211/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -30585,60 +30585,60 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1088万
 $24,716/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
 $1120万
 $25,000/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 467呎 (2房)
 $1238万
 $26,501/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $999万
 $23,233/呎
-(25年-07月-20日)</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
+(25年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>P1 | 1162呎 (4+房)
 $3650万
 $31,411/呎
-(25年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="inlineStr">
+(25年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2436万
 $28,000/呎
-(25年-12月-18日)</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
+(25年-12月-19日)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2758万
 $28,971/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -30792,18 +30792,40 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1417呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 $3652万
 $35,800/呎
-(26年-03月-11日)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+(26年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1016呎 (3房)
 -
@@ -30811,7 +30833,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 1029呎 (3房)
 -
@@ -30819,7 +30841,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 1083呎 (3房)
 -
@@ -30827,9 +30849,9 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="22" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>P2 | 2871呎 (4+房)
 -
@@ -30837,29 +30859,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1417呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr"/>
-      <c r="I6" s="22" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -30867,31 +30867,31 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1245万
 $25,619/呎
-(25年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
+(25年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1138万
 $23,474/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1137万
 $23,161/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1804万
@@ -30899,8 +30899,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30908,7 +30908,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30916,7 +30916,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30924,40 +30924,40 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1180万
 $24,274/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1556万
 $32,089/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1196万
 $24,365/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1532万
 $32,191/呎
-(26年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="20" t="inlineStr">
+(26年-06月-18日)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30965,7 +30965,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30973,7 +30973,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -30981,56 +30981,56 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1543万
 $31,745/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
+(26年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1169万
 $24,095/呎
-(25年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
+(25年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1174万
 $23,906/呎
-(25年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+(25年-07月-25日)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1137万
 $23,895/呎
-(25年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr">
+(25年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6754万
 $47,500/呎
-(25年-11月-30日)</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
+(25年-12月-01日)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $8574万
 $55,000/呎
-(26年-02月-11日)</t>
-        </is>
-      </c>
-      <c r="I9" s="22" t="inlineStr"/>
+(26年-02月-12日)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31038,56 +31038,56 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1170万
 $24,078/呎
-(25年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
+(25年-07月-22日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1112万
 $22,926/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1116万
 $22,723/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1081万
 $22,714/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6086万
 $42,800/呎
-(25年-09月-08日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
+(25年-09月-09日)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $7592万
 $48,700/呎
-(25年-08月-11日)</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr"/>
+(25年-08月-12日)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -31095,56 +31095,56 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1084万
 $22,307/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1081万
 $22,287/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1276万
 $25,982/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1064万
 $22,357/呎
-(25年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr">
+(25年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5644万
 $39,690/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6715万
 $43,071/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr"/>
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -31152,56 +31152,56 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1081万
 $22,251/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1078万
 $22,231/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1082万
 $22,035/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1048万
 $22,027/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5431万
 $38,190/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6324万
 $40,565/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr"/>
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -31209,56 +31209,56 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1065万
 $21,922/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1128万
 $23,256/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1132万
 $23,051/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $998万
 $20,958/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5404万
 $38,000/呎
-(25年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
+(25年-07月-25日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6018万
 $38,602/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I13" s="22" t="inlineStr"/>
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -31266,56 +31266,56 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1046万
 $21,523/呎
-(25年-06月-19日)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+(25年-06月-20日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1108万
 $22,847/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1046万
 $21,314/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $993万
 $20,855/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5494万
 $38,634/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6220万
 $39,900/呎
-(25年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr"/>
+(25年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -31323,56 +31323,56 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1040万
 $21,395/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1102万
 $22,713/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1040万
 $21,187/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
 $20,750/呎
-(25年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr">
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5052万
 $35,530/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5850万
 $37,525/呎
-(25年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr"/>
+(25年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -31380,56 +31380,56 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
 $21,267/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1030万
 $21,247/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1099万
 $22,377/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $983万
 $20,647/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4996万
 $35,136/呎
-(25年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
+(25年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5791万
 $37,145/呎
-(25年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr"/>
+(25年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -31437,56 +31437,56 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1027万
 $21,140/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1024万
 $21,122/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1028万
 $20,937/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $978万
 $20,546/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4839万
 $34,028/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5609万
 $35,977/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr"/>
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -31494,68 +31494,68 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
 $22,282/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1063万
 $21,915/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1005万
 $20,506/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $964万
 $20,261/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $917万
 $20,160/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3273万
 $35,350/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2726万
 $31,700/呎
-(25年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
+(25年-07月-31日)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2494万
 $30,200/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
     </row>
@@ -31565,68 +31565,68 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1015万
 $20,889/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1059万
 $21,829/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1063万
 $21,700/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $961万
 $20,181/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $971万
 $21,334/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3084万
 $33,300/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2582万
 $30,020/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2591万
 $31,368/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -31636,68 +31636,68 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1011万
 $20,807/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1054万
 $21,742/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1059万
 $21,614/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $957万
 $20,101/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $910万
 $20,000/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3337万
 $36,040/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2541万
 $29,545/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2548万
 $30,850/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -31707,68 +31707,68 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1070万
 $22,016/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1050万
 $21,656/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $993万
 $20,261/呎
-(25年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+(25年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1012万
 $21,271/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $906万
 $19,921/呎
-(25年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+(25年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3300万
 $35,639/呎
-(25年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
+(25年-06月-27日)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2500万
 $29,070/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2519万
 $30,500/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -31778,68 +31778,68 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1003万
 $20,640/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $984万
 $20,299/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $989万
 $20,180/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $949万
 $19,941/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $903万
 $19,842/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2824万
 $30,495/呎
-(25年-06月-18日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+(25年-06月-19日)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2623万
 $30,500/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2490万
 $30,150/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -31849,68 +31849,68 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1062万
 $21,842/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $981万
 $20,219/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $985万
 $20,100/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $945万
 $19,861/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $955万
 $20,998/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2784万
 $30,068/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2487万
 $28,916/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2437万
 $29,500/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -31920,68 +31920,68 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
 $20,220/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $977万
 $20,140/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1042万
 $21,269/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $942万
 $19,782/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $896万
 $19,684/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3217万
 $34,740/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2482万
 $28,856/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2342万
 $28,350/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -31991,68 +31991,68 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1053万
 $21,669/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $973万
 $20,058/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $977万
 $19,941/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $996万
 $20,935/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $892万
 $19,604/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3045万
 $32,880/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2451万
 $28,500/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2321万
 $28,100/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
     </row>
@@ -32062,68 +32062,68 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $987万
 $20,313/呎
-(25年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
+(25年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $969万
 $19,977/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1034万
 $21,102/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $934万
 $19,624/呎
-(25年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
+(25年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $888万
 $19,525/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2727万
 $29,450/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2426万
 $28,215/呎
-(25年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
+(25年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2310万
 $27,970/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -32133,68 +32133,68 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
 $20,233/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $965万
 $19,899/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $969万
 $19,780/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
 $20,767/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $885万
 $19,448/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2701万
 $29,165/呎
-(25年-07月-14日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
+(25年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2402万
 $27,930/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2294万
 $27,770/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -32204,68 +32204,68 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $979万
 $20,152/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $949万
 $19,571/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $965万
 $19,702/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $927万
 $19,468/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $926万
 $20,341/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2674万
 $28,880/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2498万
 $29,041/呎
-(25年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="inlineStr">
+(25年-07月-25日)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2277万
 $27,570/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -32275,68 +32275,68 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $976万
 $20,072/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $957万
 $19,740/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $962万
 $19,624/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $981万
 $20,603/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $878万
 $19,295/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2787万
 $30,100/呎
-(25年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
+(25年-07月-14日)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2555万
 $29,713/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
+(25年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2355万
 $28,511/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -32346,68 +32346,68 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1032万
 $21,241/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1013万
 $20,891/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1018万
 $20,767/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $919万
 $19,313/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $874万
 $19,218/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2622万
 $28,310/呎
-(25年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2378万
 $27,650/呎
-(25年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
+(25年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2244万
 $27,169/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -32417,68 +32417,68 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1028万
 $21,156/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1009万
 $20,808/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1014万
 $20,686/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $916万
 $19,235/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
 $19,141/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2734万
 $29,526/呎
-(25年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
+(25年-08月-11日)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2382万
 $27,700/呎
-(25年-08月-20日)</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
+(25年-08月-21日)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2304万
 $27,900/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -32488,68 +32488,68 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1024万
 $21,072/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $934万
 $19,262/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $950万
 $19,390/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $969万
 $20,357/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
 $19,064/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2715万
 $29,316/呎
-(25年-07月-31日)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
+(25年-08月-01日)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
 $27,500/呎
-(25年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
+(25年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2211万
 $26,770/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -32559,68 +32559,68 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1020万
 $20,988/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1001万
 $20,643/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $946万
 $19,314/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $908万
 $19,084/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $864万
 $18,989/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2584万
 $27,900/呎
-(25年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="H33" s="21" t="inlineStr">
+(25年-08月-11日)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2348万
 $27,300/呎
-(25年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="I33" s="21" t="inlineStr">
+(25年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2272万
 $27,500/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -32630,68 +32630,68 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1016万
 $20,905/呎
-(25年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
+(25年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $938万
 $19,351/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $943万
 $19,237/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $905万
 $19,008/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $914万
 $20,095/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
+(25年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2565万
 $27,700/呎
-(25年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
+(25年-09月-17日)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2331万
 $27,100/呎
-(25年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
+(25年-09月-17日)</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2296万
 $27,800/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -32701,68 +32701,68 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $952万
 $19,597/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $993万
 $20,478/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $939万
 $19,159/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $901万
 $18,933/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $911万
 $20,013/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2680万
 $28,947/呎
-(25年-09月-02日)</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
+(25年-09月-03日)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2313万
 $26,895/呎
-(25年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2280万
 $27,599/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -32772,68 +32772,68 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $949万
 $19,519/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $931万
 $19,196/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $935万
 $19,084/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $954万
 $20,036/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $854万
 $18,763/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2556万
 $27,600/呎
-(25年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
+(25年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2339万
 $27,200/呎
-(25年-10月-14日)</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
+(25年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2263万
 $27,400/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -32843,68 +32843,68 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $945万
 $19,440/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $927万
 $19,120/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $931万
 $19,006/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $894万
 $18,782/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $850万
 $18,688/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2574万
 $27,800/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
 $27,500/呎
-(25年-10月-20日)</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
+(25年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2247万
 $27,200/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -32914,68 +32914,68 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1158万
 $26,316/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 439呎 (2房)
 $1089万
 $24,800/呎
-(25年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 444呎 (2房)
 $1092万
 $24,599/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $1182万
 $27,500/呎
-(25年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $1040万
 $25,500/呎
-(25年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="inlineStr">
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2546万
 $27,499/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
+(25年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2471万
 $28,737/呎
-(25年-10月-21日)</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
+(25年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2354万
 $28,500/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -262,13 +262,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -28720,14 +28720,56 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1020呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1034呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 1083呎 (3房)
+$3890万
+$35,921/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 3120呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28735,50 +28777,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 1020呎 (3房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1034呎 (3房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>C | 1083呎 (3房)
-$3890万
-$35,921/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>P2 | 3120呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -28786,7 +28786,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1593万
@@ -28794,7 +28794,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1142万
@@ -28802,7 +28802,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1235万
@@ -28810,8 +28810,8 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28819,7 +28819,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 -
@@ -28827,7 +28827,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -28835,7 +28835,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1566万
@@ -28843,7 +28843,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1130万
@@ -28851,7 +28851,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1276万
@@ -28859,8 +28859,8 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28868,7 +28868,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $10775万
@@ -28876,7 +28876,7 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="H8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -28884,7 +28884,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1429万
@@ -28892,7 +28892,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1227万
@@ -28900,7 +28900,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1245万
@@ -28908,8 +28908,8 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $7296万
@@ -28917,7 +28917,7 @@
 (25年-11月-06日)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8530万
@@ -28925,7 +28925,7 @@
 (25年-06月-26日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="H9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -28933,7 +28933,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1117万
@@ -28941,7 +28941,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1131万
@@ -28949,7 +28949,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1154万
@@ -28957,8 +28957,8 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6543万
@@ -28966,7 +28966,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8189万
@@ -28974,7 +28974,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="H10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1086万
@@ -28990,7 +28990,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1100万
@@ -28998,7 +28998,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1217万
@@ -29006,8 +29006,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr"/>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6420万
@@ -29015,7 +29015,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7558万
@@ -29023,7 +29023,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="H11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -29031,7 +29031,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -29039,7 +29039,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1097万
@@ -29047,7 +29047,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1137万
@@ -29055,8 +29055,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6298万
@@ -29064,7 +29064,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7421万
@@ -29072,7 +29072,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
+      <c r="H12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -29080,7 +29080,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1067万
@@ -29088,7 +29088,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1081万
@@ -29096,7 +29096,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1128万
@@ -29104,8 +29104,8 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6089万
@@ -29113,7 +29113,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7319万
@@ -29121,7 +29121,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -29129,7 +29129,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1048万
@@ -29137,7 +29137,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1061万
@@ -29145,7 +29145,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1123万
@@ -29153,8 +29153,8 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5990万
@@ -29162,7 +29162,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6726万
@@ -29170,7 +29170,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr"/>
+      <c r="H14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -29178,7 +29178,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1107万
@@ -29186,7 +29186,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1055万
@@ -29194,7 +29194,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1187万
@@ -29202,8 +29202,8 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5574万
@@ -29211,7 +29211,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6596万
@@ -29219,7 +29219,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -29227,7 +29227,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1100万
@@ -29235,7 +29235,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1114万
@@ -29243,7 +29243,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1112万
@@ -29251,8 +29251,8 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5076万
@@ -29260,7 +29260,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6467万
@@ -29268,7 +29268,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr"/>
+      <c r="H16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1094万
@@ -29284,7 +29284,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1108万
@@ -29292,7 +29292,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1175万
@@ -29300,8 +29300,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>P1 | 1469呎 (4+房)
 $5739万
@@ -29309,7 +29309,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6739万
@@ -29317,7 +29317,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr"/>
+      <c r="H17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -29325,7 +29325,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1025万
@@ -29333,7 +29333,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1036万
@@ -29341,7 +29341,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1084万
@@ -29349,7 +29349,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1011万
@@ -29357,7 +29357,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>P1 | 1258呎 (4+房)
 $4422万
@@ -29365,7 +29365,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2694万
@@ -29373,7 +29373,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3313万
@@ -29388,7 +29388,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1021万
@@ -29396,7 +29396,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1032万
@@ -29404,7 +29404,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1066万
@@ -29412,7 +29412,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1005万
@@ -29420,7 +29420,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4351万
@@ -29428,7 +29428,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2653万
@@ -29436,7 +29436,7 @@
 (25年-06月-30日)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3447万
@@ -29451,7 +29451,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1017万
@@ -29459,7 +29459,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1028万
@@ -29467,7 +29467,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1076万
@@ -29475,7 +29475,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $999万
@@ -29483,7 +29483,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4540万
@@ -29491,7 +29491,7 @@
 (25年-06月-26日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2612万
@@ -29499,7 +29499,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3256万
@@ -29514,7 +29514,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1013万
@@ -29522,7 +29522,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1024万
@@ -29530,7 +29530,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1138万
@@ -29538,7 +29538,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $993万
@@ -29546,7 +29546,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4265万
@@ -29554,7 +29554,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2579万
@@ -29562,7 +29562,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3220万
@@ -29577,7 +29577,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1009万
@@ -29585,7 +29585,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1020万
@@ -29593,7 +29593,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1067万
@@ -29601,7 +29601,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $987万
@@ -29609,7 +29609,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4229万
@@ -29617,7 +29617,7 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2688万
@@ -29625,7 +29625,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3056万
@@ -29640,7 +29640,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1005万
@@ -29648,7 +29648,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1079万
@@ -29656,7 +29656,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1063万
@@ -29664,7 +29664,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $984万
@@ -29672,7 +29672,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4193万
@@ -29680,7 +29680,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2529万
@@ -29688,7 +29688,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2876万
@@ -29703,7 +29703,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1001万
@@ -29711,7 +29711,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1008万
@@ -29719,7 +29719,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1059万
@@ -29727,7 +29727,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $980万
@@ -29735,7 +29735,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4184万
@@ -29743,7 +29743,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2504万
@@ -29751,7 +29751,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3299万
@@ -29766,7 +29766,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $997万
@@ -29774,7 +29774,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1004万
@@ -29782,7 +29782,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1113万
@@ -29790,7 +29790,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1037万
@@ -29798,7 +29798,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4374万
@@ -29806,7 +29806,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2480万
@@ -29814,7 +29814,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3122万
@@ -29829,7 +29829,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $993万
@@ -29837,7 +29837,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1000万
@@ -29845,7 +29845,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1043万
@@ -29853,7 +29853,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $972万
@@ -29861,7 +29861,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3725万
@@ -29869,7 +29869,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2406万
@@ -29877,7 +29877,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2893万
@@ -29892,7 +29892,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $989万
@@ -29900,7 +29900,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $996万
@@ -29908,7 +29908,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1039万
@@ -29916,7 +29916,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $968万
@@ -29924,7 +29924,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3680万
@@ -29932,7 +29932,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2526万
@@ -29940,7 +29940,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2850万
@@ -29955,7 +29955,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $985万
@@ -29963,7 +29963,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $992万
@@ -29971,7 +29971,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1022万
@@ -29979,7 +29979,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1024万
@@ -29987,7 +29987,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3955万
@@ -29995,7 +29995,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2349万
@@ -30003,7 +30003,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2652万
@@ -30018,7 +30018,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $981万
@@ -30026,7 +30026,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1049万
@@ -30034,7 +30034,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1095万
@@ -30042,7 +30042,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
@@ -30050,7 +30050,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3818万
@@ -30058,7 +30058,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2319万
@@ -30066,7 +30066,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2784万
@@ -30081,7 +30081,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1038万
@@ -30089,7 +30089,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1045万
@@ -30097,7 +30097,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1091万
@@ -30105,7 +30105,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
@@ -30113,7 +30113,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3862万
@@ -30121,7 +30121,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2396万
@@ -30129,7 +30129,7 @@
 (25年-08月-06日)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2708万
@@ -30144,7 +30144,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -30152,7 +30152,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1041万
@@ -30160,7 +30160,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1086万
@@ -30168,7 +30168,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $952万
@@ -30176,7 +30176,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3819万
@@ -30184,7 +30184,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2361万
@@ -30192,7 +30192,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2668万
@@ -30207,7 +30207,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1030万
@@ -30215,7 +30215,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $976万
@@ -30223,7 +30223,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1006万
@@ -30231,7 +30231,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $949万
@@ -30239,7 +30239,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3785万
@@ -30247,7 +30247,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2338万
@@ -30255,7 +30255,7 @@
 (25年-09月-18日)</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2641万
@@ -30270,7 +30270,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1026万
@@ -30278,7 +30278,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1033万
@@ -30286,7 +30286,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1014万
@@ -30294,7 +30294,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $945万
@@ -30302,7 +30302,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3474万
@@ -30310,7 +30310,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2306万
@@ -30318,7 +30318,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2578万
@@ -30333,7 +30333,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $962万
@@ -30341,7 +30341,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $968万
@@ -30349,7 +30349,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1010万
@@ -30357,7 +30357,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
@@ -30365,7 +30365,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3632万
@@ -30373,7 +30373,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2392万
@@ -30381,7 +30381,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2586万
@@ -30396,7 +30396,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1018万
@@ -30404,7 +30404,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $964万
@@ -30412,7 +30412,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1069万
@@ -30420,7 +30420,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
@@ -30428,7 +30428,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3426万
@@ -30436,7 +30436,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2399万
@@ -30444,7 +30444,7 @@
 (25年-08月-26日)</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2675万
@@ -30459,7 +30459,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1014万
@@ -30467,7 +30467,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $960万
@@ -30475,7 +30475,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1002万
@@ -30483,7 +30483,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $976万
@@ -30491,7 +30491,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3881万
@@ -30499,7 +30499,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2314万
@@ -30507,7 +30507,7 @@
 (25年-09月-09日)</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2570万
@@ -30522,7 +30522,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1010万
@@ -30530,7 +30530,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $957万
@@ -30538,7 +30538,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $998万
@@ -30546,7 +30546,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $910万
@@ -30554,7 +30554,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3577万
@@ -30562,7 +30562,7 @@
 (25年-08月-06日)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2490万
@@ -30570,7 +30570,7 @@
 (25年-12月-31日)</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2686万
@@ -30585,7 +30585,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1088万
@@ -30593,7 +30593,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
 $1120万
@@ -30601,7 +30601,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 467呎 (2房)
 $1238万
@@ -30609,7 +30609,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $999万
@@ -30617,7 +30617,7 @@
 (25年-07月-21日)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>P1 | 1162呎 (4+房)
 $3650万
@@ -30625,7 +30625,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2436万
@@ -30633,7 +30633,7 @@
 (25年-12月-19日)</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2758万
@@ -30792,15 +30792,65 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1020呎 (3房)
+$3652万
+$35,800/呎
+(26年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1016呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1029呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 1083呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>P2 | 2871呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr"/>
+      <c r="D6" s="22" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>P1 | 1417呎 (4+房)
 -
@@ -30808,58 +30858,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 1020呎 (3房)
-$3652万
-$35,800/呎
-(26年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1016呎 (3房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 1029呎 (3房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 1083呎 (3房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>P2 | 2871呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="H6" s="22" t="inlineStr"/>
+      <c r="I6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -30867,7 +30867,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1245万
@@ -30875,7 +30875,7 @@
 (25年-09月-11日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1138万
@@ -30883,7 +30883,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1137万
@@ -30891,7 +30891,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1804万
@@ -30899,8 +30899,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30908,7 +30908,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30916,7 +30916,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30924,7 +30924,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1180万
@@ -30932,7 +30932,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1556万
@@ -30940,7 +30940,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1196万
@@ -30948,7 +30948,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1532万
@@ -30956,8 +30956,8 @@
 (26年-06月-18日)</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30965,7 +30965,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30973,7 +30973,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
+      <c r="I8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1543万
@@ -30989,7 +30989,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1169万
@@ -30997,7 +30997,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1174万
@@ -31005,7 +31005,7 @@
 (25年-07月-25日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1137万
@@ -31013,8 +31013,8 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6754万
@@ -31022,7 +31022,7 @@
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $8574万
@@ -31030,7 +31030,7 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
+      <c r="I9" s="22" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1170万
@@ -31046,7 +31046,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1112万
@@ -31054,7 +31054,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1116万
@@ -31062,7 +31062,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1081万
@@ -31070,8 +31070,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6086万
@@ -31079,7 +31079,7 @@
 (25年-09月-09日)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $7592万
@@ -31087,7 +31087,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
+      <c r="I10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -31095,7 +31095,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1084万
@@ -31103,7 +31103,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1081万
@@ -31111,7 +31111,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1276万
@@ -31119,7 +31119,7 @@
 (26年-02月-27日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1064万
@@ -31127,8 +31127,8 @@
 (25年-08月-04日)</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr"/>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5644万
@@ -31136,7 +31136,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6715万
@@ -31144,7 +31144,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
+      <c r="I11" s="22" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -31152,7 +31152,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1081万
@@ -31160,7 +31160,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1078万
@@ -31168,7 +31168,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1082万
@@ -31176,7 +31176,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1048万
@@ -31184,8 +31184,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5431万
@@ -31193,7 +31193,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6324万
@@ -31201,7 +31201,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
+      <c r="I12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -31209,7 +31209,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1065万
@@ -31217,7 +31217,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1128万
@@ -31225,7 +31225,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1132万
@@ -31233,7 +31233,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $998万
@@ -31241,8 +31241,8 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5404万
@@ -31250,7 +31250,7 @@
 (25年-07月-25日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6018万
@@ -31258,7 +31258,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
+      <c r="I13" s="22" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -31266,7 +31266,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1046万
@@ -31274,7 +31274,7 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1108万
@@ -31282,7 +31282,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1046万
@@ -31290,7 +31290,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $993万
@@ -31298,8 +31298,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5494万
@@ -31307,7 +31307,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6220万
@@ -31315,7 +31315,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
+      <c r="I14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -31323,7 +31323,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1040万
@@ -31331,7 +31331,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1102万
@@ -31339,7 +31339,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1040万
@@ -31347,7 +31347,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -31355,8 +31355,8 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5052万
@@ -31364,7 +31364,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5850万
@@ -31372,7 +31372,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
+      <c r="I15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -31380,7 +31380,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -31388,7 +31388,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1030万
@@ -31396,7 +31396,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1099万
@@ -31404,7 +31404,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $983万
@@ -31412,8 +31412,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4996万
@@ -31421,7 +31421,7 @@
 (25年-06月-09日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5791万
@@ -31429,7 +31429,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
+      <c r="I16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -31437,7 +31437,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1027万
@@ -31445,7 +31445,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1024万
@@ -31453,7 +31453,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1028万
@@ -31461,7 +31461,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $978万
@@ -31469,8 +31469,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr"/>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4839万
@@ -31478,7 +31478,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5609万
@@ -31486,7 +31486,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
+      <c r="I17" s="22" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -31494,7 +31494,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -31502,7 +31502,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1063万
@@ -31510,7 +31510,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1005万
@@ -31518,7 +31518,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $964万
@@ -31526,7 +31526,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $917万
@@ -31534,7 +31534,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3273万
@@ -31542,7 +31542,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2726万
@@ -31550,7 +31550,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2494万
@@ -31565,7 +31565,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1015万
@@ -31573,7 +31573,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1059万
@@ -31581,7 +31581,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1063万
@@ -31589,7 +31589,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $961万
@@ -31597,7 +31597,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $971万
@@ -31605,7 +31605,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3084万
@@ -31613,7 +31613,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2582万
@@ -31621,7 +31621,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2591万
@@ -31636,7 +31636,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1011万
@@ -31644,7 +31644,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1054万
@@ -31652,7 +31652,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1059万
@@ -31660,7 +31660,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $957万
@@ -31668,7 +31668,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $910万
@@ -31676,7 +31676,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3337万
@@ -31684,7 +31684,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2541万
@@ -31692,7 +31692,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2548万
@@ -31707,7 +31707,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1070万
@@ -31715,7 +31715,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1050万
@@ -31723,7 +31723,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $993万
@@ -31731,7 +31731,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1012万
@@ -31739,7 +31739,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $906万
@@ -31747,7 +31747,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3300万
@@ -31755,7 +31755,7 @@
 (25年-06月-27日)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2500万
@@ -31763,7 +31763,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2519万
@@ -31778,7 +31778,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1003万
@@ -31786,7 +31786,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $984万
@@ -31794,7 +31794,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $989万
@@ -31802,7 +31802,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $949万
@@ -31810,7 +31810,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $903万
@@ -31818,7 +31818,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2824万
@@ -31826,7 +31826,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2623万
@@ -31834,7 +31834,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2490万
@@ -31849,7 +31849,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1062万
@@ -31857,7 +31857,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $981万
@@ -31865,7 +31865,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $985万
@@ -31873,7 +31873,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $945万
@@ -31881,7 +31881,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $955万
@@ -31889,7 +31889,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2784万
@@ -31897,7 +31897,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2487万
@@ -31905,7 +31905,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2437万
@@ -31920,7 +31920,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -31928,7 +31928,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $977万
@@ -31936,7 +31936,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1042万
@@ -31944,7 +31944,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $942万
@@ -31952,7 +31952,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $896万
@@ -31960,7 +31960,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3217万
@@ -31968,7 +31968,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2482万
@@ -31976,7 +31976,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2342万
@@ -31991,7 +31991,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1053万
@@ -31999,7 +31999,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $973万
@@ -32007,7 +32007,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $977万
@@ -32015,7 +32015,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $996万
@@ -32023,7 +32023,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $892万
@@ -32031,7 +32031,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3045万
@@ -32039,7 +32039,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2451万
@@ -32047,7 +32047,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2321万
@@ -32062,7 +32062,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $987万
@@ -32070,7 +32070,7 @@
 (25年-06月-30日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $969万
@@ -32078,7 +32078,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1034万
@@ -32086,7 +32086,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $934万
@@ -32094,7 +32094,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $888万
@@ -32102,7 +32102,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2727万
@@ -32110,7 +32110,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2426万
@@ -32118,7 +32118,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2310万
@@ -32133,7 +32133,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -32141,7 +32141,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $965万
@@ -32149,7 +32149,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $969万
@@ -32157,7 +32157,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -32165,7 +32165,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $885万
@@ -32173,7 +32173,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2701万
@@ -32181,7 +32181,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2402万
@@ -32189,7 +32189,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2294万
@@ -32204,7 +32204,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $979万
@@ -32212,7 +32212,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $949万
@@ -32220,7 +32220,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $965万
@@ -32228,7 +32228,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $927万
@@ -32236,7 +32236,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $926万
@@ -32244,7 +32244,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2674万
@@ -32252,7 +32252,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2498万
@@ -32260,7 +32260,7 @@
 (25年-07月-25日)</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2277万
@@ -32275,7 +32275,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $976万
@@ -32283,7 +32283,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $957万
@@ -32291,7 +32291,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $962万
@@ -32299,7 +32299,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $981万
@@ -32307,7 +32307,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $878万
@@ -32315,7 +32315,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2787万
@@ -32323,7 +32323,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2555万
@@ -32331,7 +32331,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2355万
@@ -32346,7 +32346,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1032万
@@ -32354,7 +32354,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1013万
@@ -32362,7 +32362,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1018万
@@ -32370,7 +32370,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $919万
@@ -32378,7 +32378,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $874万
@@ -32386,7 +32386,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2622万
@@ -32394,7 +32394,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2378万
@@ -32402,7 +32402,7 @@
 (25年-08月-04日)</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2244万
@@ -32417,7 +32417,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1028万
@@ -32425,7 +32425,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1009万
@@ -32433,7 +32433,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1014万
@@ -32441,7 +32441,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $916万
@@ -32449,7 +32449,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -32457,7 +32457,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2734万
@@ -32465,7 +32465,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2382万
@@ -32473,7 +32473,7 @@
 (25年-08月-21日)</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2304万
@@ -32488,7 +32488,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1024万
@@ -32496,7 +32496,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $934万
@@ -32504,7 +32504,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $950万
@@ -32512,7 +32512,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $969万
@@ -32520,7 +32520,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -32528,7 +32528,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2715万
@@ -32536,7 +32536,7 @@
 (25年-08月-01日)</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32544,7 +32544,7 @@
 (25年-08月-19日)</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2211万
@@ -32559,7 +32559,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1020万
@@ -32567,7 +32567,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1001万
@@ -32575,7 +32575,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $946万
@@ -32583,7 +32583,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $908万
@@ -32591,7 +32591,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $864万
@@ -32599,7 +32599,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2584万
@@ -32607,7 +32607,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2348万
@@ -32615,7 +32615,7 @@
 (25年-08月-19日)</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2272万
@@ -32630,7 +32630,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1016万
@@ -32638,7 +32638,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $938万
@@ -32646,7 +32646,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $943万
@@ -32654,7 +32654,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $905万
@@ -32662,7 +32662,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $914万
@@ -32670,7 +32670,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2565万
@@ -32678,7 +32678,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2331万
@@ -32686,7 +32686,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2296万
@@ -32701,7 +32701,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $952万
@@ -32709,7 +32709,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $993万
@@ -32717,7 +32717,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $939万
@@ -32725,7 +32725,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $901万
@@ -32733,7 +32733,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $911万
@@ -32741,7 +32741,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2680万
@@ -32749,7 +32749,7 @@
 (25年-09月-03日)</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2313万
@@ -32757,7 +32757,7 @@
 (25年-09月-26日)</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2280万
@@ -32772,7 +32772,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $949万
@@ -32780,7 +32780,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $931万
@@ -32788,7 +32788,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $935万
@@ -32796,7 +32796,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $954万
@@ -32804,7 +32804,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $854万
@@ -32812,7 +32812,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2556万
@@ -32820,7 +32820,7 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2339万
@@ -32828,7 +32828,7 @@
 (25年-10月-15日)</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2263万
@@ -32843,7 +32843,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $945万
@@ -32851,7 +32851,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $927万
@@ -32859,7 +32859,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $931万
@@ -32867,7 +32867,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $894万
@@ -32875,7 +32875,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $850万
@@ -32883,7 +32883,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2574万
@@ -32891,7 +32891,7 @@
 (25年-10月-09日)</t>
         </is>
       </c>
-      <c r="H37" s="22" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32899,7 +32899,7 @@
 (25年-10月-21日)</t>
         </is>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2247万
@@ -32914,7 +32914,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1158万
@@ -32922,7 +32922,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>B | 439呎 (2房)
 $1089万
@@ -32930,7 +32930,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 444呎 (2房)
 $1092万
@@ -32938,7 +32938,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $1182万
@@ -32946,7 +32946,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $1040万
@@ -32954,7 +32954,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2546万
@@ -32962,7 +32962,7 @@
 (25年-10月-10日)</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2471万
@@ -32970,7 +32970,7 @@
 (25年-10月-22日)</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2354万

--- a/files/港岛-黄竹坑-滶晨.xlsx
+++ b/files/港岛-黄竹坑-滶晨.xlsx
@@ -262,13 +262,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -28720,10 +28720,31 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1536呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 -
@@ -28731,7 +28752,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1034呎 (3房)
 -
@@ -28739,7 +28760,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 1083呎 (3房)
 $3890万
@@ -28747,9 +28768,9 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>P2 | 3120呎 (4+房)
 -
@@ -28757,19 +28778,40 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 486呎 (2房)
+$1593万
+$32,776/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 494呎 (2房)
+$1142万
+$23,109/呎
+(25年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 517呎 (2房)
+$1235万
+$23,892/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28777,41 +28819,48 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>P2 | 1706呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
-$1593万
-$32,776/呎
-(26年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
+$1566万
+$32,222/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
-$1142万
-$23,109/呎
-(25年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
+$1130万
+$22,881/呎
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
-$1235万
-$23,892/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+$1276万
+$24,689/呎
+(25年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 -
@@ -28819,56 +28868,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>P2 | 1706呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 486呎 (2房)
-$1566万
-$32,222/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 494呎 (2房)
-$1130万
-$22,881/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 517呎 (2房)
-$1276万
-$24,689/呎
-(25年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1536呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $10775万
@@ -28876,7 +28876,7 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -28884,7 +28884,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1429万
@@ -28892,7 +28892,7 @@
 (26年-03月-06日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1227万
@@ -28900,7 +28900,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1245万
@@ -28908,8 +28908,8 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr"/>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $7296万
@@ -28917,7 +28917,7 @@
 (25年-11月-06日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8530万
@@ -28925,7 +28925,7 @@
 (25年-06月-26日)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -28933,7 +28933,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1117万
@@ -28941,7 +28941,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1131万
@@ -28949,7 +28949,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1154万
@@ -28957,8 +28957,8 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr"/>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6543万
@@ -28966,7 +28966,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $8189万
@@ -28974,7 +28974,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1086万
@@ -28990,7 +28990,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1100万
@@ -28998,7 +28998,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1217万
@@ -29006,8 +29006,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr"/>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6420万
@@ -29015,7 +29015,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7558万
@@ -29023,7 +29023,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -29031,7 +29031,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -29039,7 +29039,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1097万
@@ -29047,7 +29047,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1137万
@@ -29055,8 +29055,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr"/>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6298万
@@ -29064,7 +29064,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7421万
@@ -29072,7 +29072,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -29080,7 +29080,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1067万
@@ -29088,7 +29088,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1081万
@@ -29096,7 +29096,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1128万
@@ -29104,8 +29104,8 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr"/>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $6089万
@@ -29113,7 +29113,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $7319万
@@ -29121,7 +29121,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -29129,7 +29129,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1048万
@@ -29137,7 +29137,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1061万
@@ -29145,7 +29145,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1123万
@@ -29153,8 +29153,8 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr"/>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5990万
@@ -29162,7 +29162,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6726万
@@ -29170,7 +29170,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -29178,7 +29178,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1107万
@@ -29186,7 +29186,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1055万
@@ -29194,7 +29194,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1187万
@@ -29202,8 +29202,8 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr"/>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5574万
@@ -29211,7 +29211,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6596万
@@ -29219,7 +29219,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -29227,7 +29227,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1100万
@@ -29235,7 +29235,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1114万
@@ -29243,7 +29243,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1112万
@@ -29251,8 +29251,8 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr"/>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1536呎 (4+房)
 $5076万
@@ -29260,7 +29260,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6467万
@@ -29268,7 +29268,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1094万
@@ -29284,7 +29284,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1108万
@@ -29292,7 +29292,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1175万
@@ -29300,8 +29300,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr"/>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1469呎 (4+房)
 $5739万
@@ -29309,7 +29309,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1706呎 (4+房)
 $6739万
@@ -29317,7 +29317,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -29325,7 +29325,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1025万
@@ -29333,7 +29333,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1036万
@@ -29341,7 +29341,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1084万
@@ -29349,7 +29349,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1011万
@@ -29357,7 +29357,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>P1 | 1258呎 (4+房)
 $4422万
@@ -29365,7 +29365,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2694万
@@ -29373,7 +29373,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3313万
@@ -29388,7 +29388,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1021万
@@ -29396,7 +29396,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1032万
@@ -29404,7 +29404,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1066万
@@ -29412,7 +29412,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1005万
@@ -29420,7 +29420,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4351万
@@ -29428,7 +29428,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2653万
@@ -29436,7 +29436,7 @@
 (25年-06月-30日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3447万
@@ -29451,7 +29451,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1017万
@@ -29459,7 +29459,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1028万
@@ -29467,7 +29467,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1076万
@@ -29475,7 +29475,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $999万
@@ -29483,7 +29483,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4540万
@@ -29491,7 +29491,7 @@
 (25年-06月-26日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2612万
@@ -29499,7 +29499,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3256万
@@ -29514,7 +29514,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1013万
@@ -29522,7 +29522,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1024万
@@ -29530,7 +29530,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1138万
@@ -29538,7 +29538,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $993万
@@ -29546,7 +29546,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4265万
@@ -29554,7 +29554,7 @@
 (25年-06月-12日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2579万
@@ -29562,7 +29562,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3220万
@@ -29577,7 +29577,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1009万
@@ -29585,7 +29585,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1020万
@@ -29593,7 +29593,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1067万
@@ -29601,7 +29601,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $987万
@@ -29609,7 +29609,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4229万
@@ -29617,7 +29617,7 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2688万
@@ -29625,7 +29625,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3056万
@@ -29640,7 +29640,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1005万
@@ -29648,7 +29648,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1079万
@@ -29656,7 +29656,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1063万
@@ -29664,7 +29664,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $984万
@@ -29672,7 +29672,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4193万
@@ -29680,7 +29680,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2529万
@@ -29688,7 +29688,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2876万
@@ -29703,7 +29703,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1001万
@@ -29711,7 +29711,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1008万
@@ -29719,7 +29719,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1059万
@@ -29727,7 +29727,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $980万
@@ -29735,7 +29735,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4184万
@@ -29743,7 +29743,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2504万
@@ -29751,7 +29751,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3299万
@@ -29766,7 +29766,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $997万
@@ -29774,7 +29774,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1004万
@@ -29782,7 +29782,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1113万
@@ -29790,7 +29790,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1037万
@@ -29798,7 +29798,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $4374万
@@ -29806,7 +29806,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2480万
@@ -29814,7 +29814,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $3122万
@@ -29829,7 +29829,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $993万
@@ -29837,7 +29837,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1000万
@@ -29845,7 +29845,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1043万
@@ -29853,7 +29853,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $972万
@@ -29861,7 +29861,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3725万
@@ -29869,7 +29869,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2406万
@@ -29877,7 +29877,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2893万
@@ -29892,7 +29892,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $989万
@@ -29900,7 +29900,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $996万
@@ -29908,7 +29908,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1039万
@@ -29916,7 +29916,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $968万
@@ -29924,7 +29924,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3680万
@@ -29932,7 +29932,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2526万
@@ -29940,7 +29940,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2850万
@@ -29955,7 +29955,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $985万
@@ -29963,7 +29963,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $992万
@@ -29971,7 +29971,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1022万
@@ -29979,7 +29979,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $1024万
@@ -29987,7 +29987,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3955万
@@ -29995,7 +29995,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2349万
@@ -30003,7 +30003,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2652万
@@ -30018,7 +30018,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $981万
@@ -30026,7 +30026,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1049万
@@ -30034,7 +30034,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1095万
@@ -30042,7 +30042,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $948万
@@ -30050,7 +30050,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3818万
@@ -30058,7 +30058,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2319万
@@ -30066,7 +30066,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2784万
@@ -30081,7 +30081,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1038万
@@ -30089,7 +30089,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1045万
@@ -30097,7 +30097,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1091万
@@ -30105,7 +30105,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $956万
@@ -30113,7 +30113,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3862万
@@ -30121,7 +30121,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2396万
@@ -30129,7 +30129,7 @@
 (25年-08月-06日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2708万
@@ -30144,7 +30144,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -30152,7 +30152,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1041万
@@ -30160,7 +30160,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1086万
@@ -30168,7 +30168,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $952万
@@ -30176,7 +30176,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3819万
@@ -30184,7 +30184,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2361万
@@ -30192,7 +30192,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2668万
@@ -30207,7 +30207,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1030万
@@ -30215,7 +30215,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $976万
@@ -30223,7 +30223,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1006万
@@ -30231,7 +30231,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $949万
@@ -30239,7 +30239,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3785万
@@ -30247,7 +30247,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2338万
@@ -30255,7 +30255,7 @@
 (25年-09月-18日)</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2641万
@@ -30270,7 +30270,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1026万
@@ -30278,7 +30278,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $1033万
@@ -30286,7 +30286,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1014万
@@ -30294,7 +30294,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $945万
@@ -30302,7 +30302,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3474万
@@ -30310,7 +30310,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2306万
@@ -30318,7 +30318,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2578万
@@ -30333,7 +30333,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $962万
@@ -30341,7 +30341,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $968万
@@ -30349,7 +30349,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1010万
@@ -30357,7 +30357,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $938万
@@ -30365,7 +30365,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3632万
@@ -30373,7 +30373,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2392万
@@ -30381,7 +30381,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2586万
@@ -30396,7 +30396,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1018万
@@ -30404,7 +30404,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $964万
@@ -30412,7 +30412,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1069万
@@ -30420,7 +30420,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $928万
@@ -30428,7 +30428,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3426万
@@ -30436,7 +30436,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2399万
@@ -30444,7 +30444,7 @@
 (25年-08月-26日)</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2675万
@@ -30459,7 +30459,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1014万
@@ -30467,7 +30467,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $960万
@@ -30475,7 +30475,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $1002万
@@ -30483,7 +30483,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $976万
@@ -30491,7 +30491,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3881万
@@ -30499,7 +30499,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2314万
@@ -30507,7 +30507,7 @@
 (25年-09月-09日)</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2570万
@@ -30522,7 +30522,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1010万
@@ -30530,7 +30530,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 494呎 (2房)
 $957万
@@ -30538,7 +30538,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 517呎 (2房)
 $998万
@@ -30546,7 +30546,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 477呎 (2房)
 $910万
@@ -30554,7 +30554,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>P1 | 1261呎 (4+房)
 $3577万
@@ -30562,7 +30562,7 @@
 (25年-08月-06日)</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2490万
@@ -30570,7 +30570,7 @@
 (25年-12月-31日)</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2686万
@@ -30585,7 +30585,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1088万
@@ -30593,7 +30593,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
 $1120万
@@ -30601,7 +30601,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 467呎 (2房)
 $1238万
@@ -30609,7 +30609,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $999万
@@ -30617,7 +30617,7 @@
 (25年-07月-21日)</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>P1 | 1162呎 (4+房)
 $3650万
@@ -30625,7 +30625,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P2 | 870呎 (3房)
 $2436万
@@ -30633,7 +30633,7 @@
 (25年-12月-19日)</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P3 | 952呎 (3房)
 $2758万
@@ -30792,10 +30792,32 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>P1 | 1417呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1020呎 (3房)
 $3652万
@@ -30803,7 +30825,7 @@
 (26年-03月-12日)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1016呎 (3房)
 -
@@ -30811,7 +30833,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 1029呎 (3房)
 -
@@ -30819,7 +30841,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 1083呎 (3房)
 -
@@ -30827,9 +30849,9 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="22" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>P2 | 2871呎 (4+房)
 -
@@ -30837,29 +30859,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>P1 | 1417呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr"/>
-      <c r="I6" s="22" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -30867,7 +30867,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1245万
@@ -30875,7 +30875,7 @@
 (25年-09月-11日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1138万
@@ -30883,7 +30883,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1137万
@@ -30891,7 +30891,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1804万
@@ -30899,8 +30899,8 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30908,7 +30908,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30916,7 +30916,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -30924,7 +30924,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1180万
@@ -30932,7 +30932,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1556万
@@ -30940,7 +30940,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1196万
@@ -30948,7 +30948,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1532万
@@ -30956,8 +30956,8 @@
 (26年-06月-18日)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 -
@@ -30965,7 +30965,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 -
@@ -30973,7 +30973,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1543万
@@ -30989,7 +30989,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1169万
@@ -30997,7 +30997,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1174万
@@ -31005,7 +31005,7 @@
 (25年-07月-25日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1137万
@@ -31013,8 +31013,8 @@
 (25年-07月-24日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6754万
@@ -31022,7 +31022,7 @@
 (25年-12月-01日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $8574万
@@ -31030,7 +31030,7 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -31038,7 +31038,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1170万
@@ -31046,7 +31046,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1112万
@@ -31054,7 +31054,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1116万
@@ -31062,7 +31062,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1081万
@@ -31070,8 +31070,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $6086万
@@ -31079,7 +31079,7 @@
 (25年-09月-09日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $7592万
@@ -31087,7 +31087,7 @@
 (25年-08月-12日)</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -31095,7 +31095,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1084万
@@ -31103,7 +31103,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1081万
@@ -31111,7 +31111,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1276万
@@ -31119,7 +31119,7 @@
 (26年-02月-27日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1064万
@@ -31127,8 +31127,8 @@
 (25年-08月-04日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5644万
@@ -31136,7 +31136,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6715万
@@ -31144,7 +31144,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -31152,7 +31152,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1081万
@@ -31160,7 +31160,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1078万
@@ -31168,7 +31168,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1082万
@@ -31176,7 +31176,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1048万
@@ -31184,8 +31184,8 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5431万
@@ -31193,7 +31193,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6324万
@@ -31201,7 +31201,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -31209,7 +31209,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1065万
@@ -31217,7 +31217,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1128万
@@ -31225,7 +31225,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1132万
@@ -31233,7 +31233,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $998万
@@ -31241,8 +31241,8 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5404万
@@ -31250,7 +31250,7 @@
 (25年-07月-25日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6018万
@@ -31258,7 +31258,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -31266,7 +31266,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1046万
@@ -31274,7 +31274,7 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1108万
@@ -31282,7 +31282,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1046万
@@ -31290,7 +31290,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $993万
@@ -31298,8 +31298,8 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5494万
@@ -31307,7 +31307,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $6220万
@@ -31315,7 +31315,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -31323,7 +31323,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1040万
@@ -31331,7 +31331,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1102万
@@ -31339,7 +31339,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1040万
@@ -31347,7 +31347,7 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -31355,8 +31355,8 @@
 (25年-07月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $5052万
@@ -31364,7 +31364,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5850万
@@ -31372,7 +31372,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -31380,7 +31380,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1034万
@@ -31388,7 +31388,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1030万
@@ -31396,7 +31396,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1099万
@@ -31404,7 +31404,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $983万
@@ -31412,8 +31412,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4996万
@@ -31421,7 +31421,7 @@
 (25年-06月-09日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5791万
@@ -31429,7 +31429,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -31437,7 +31437,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1027万
@@ -31445,7 +31445,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1024万
@@ -31453,7 +31453,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 491呎 (2房)
 $1028万
@@ -31461,7 +31461,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $978万
@@ -31469,8 +31469,8 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr"/>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>P1 | 1422呎 (4+房)
 $4839万
@@ -31478,7 +31478,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>P2 | 1559呎 (4+房)
 $5609万
@@ -31486,7 +31486,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -31494,7 +31494,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1083万
@@ -31502,7 +31502,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1063万
@@ -31510,7 +31510,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1005万
@@ -31518,7 +31518,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $964万
@@ -31526,7 +31526,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $917万
@@ -31534,7 +31534,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3273万
@@ -31542,7 +31542,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2726万
@@ -31550,7 +31550,7 @@
 (25年-07月-31日)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2494万
@@ -31565,7 +31565,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1015万
@@ -31573,7 +31573,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1059万
@@ -31581,7 +31581,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1063万
@@ -31589,7 +31589,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $961万
@@ -31597,7 +31597,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $971万
@@ -31605,7 +31605,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3084万
@@ -31613,7 +31613,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2582万
@@ -31621,7 +31621,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2591万
@@ -31636,7 +31636,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1011万
@@ -31644,7 +31644,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1054万
@@ -31652,7 +31652,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1059万
@@ -31660,7 +31660,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $957万
@@ -31668,7 +31668,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $910万
@@ -31676,7 +31676,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3337万
@@ -31684,7 +31684,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2541万
@@ -31692,7 +31692,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2548万
@@ -31707,7 +31707,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1070万
@@ -31715,7 +31715,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1050万
@@ -31723,7 +31723,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $993万
@@ -31731,7 +31731,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $1012万
@@ -31739,7 +31739,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $906万
@@ -31747,7 +31747,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3300万
@@ -31755,7 +31755,7 @@
 (25年-06月-27日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2500万
@@ -31763,7 +31763,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2519万
@@ -31778,7 +31778,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1003万
@@ -31786,7 +31786,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $984万
@@ -31794,7 +31794,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $989万
@@ -31802,7 +31802,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $949万
@@ -31810,7 +31810,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $903万
@@ -31818,7 +31818,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2824万
@@ -31826,7 +31826,7 @@
 (25年-06月-19日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2623万
@@ -31834,7 +31834,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2490万
@@ -31849,7 +31849,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1062万
@@ -31857,7 +31857,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $981万
@@ -31865,7 +31865,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $985万
@@ -31873,7 +31873,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $945万
@@ -31881,7 +31881,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $955万
@@ -31889,7 +31889,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2784万
@@ -31897,7 +31897,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2487万
@@ -31905,7 +31905,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2437万
@@ -31920,7 +31920,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -31928,7 +31928,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $977万
@@ -31936,7 +31936,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1042万
@@ -31944,7 +31944,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $942万
@@ -31952,7 +31952,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $896万
@@ -31960,7 +31960,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3217万
@@ -31968,7 +31968,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2482万
@@ -31976,7 +31976,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2342万
@@ -31991,7 +31991,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1053万
@@ -31999,7 +31999,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $973万
@@ -32007,7 +32007,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $977万
@@ -32015,7 +32015,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $996万
@@ -32023,7 +32023,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $892万
@@ -32031,7 +32031,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $3045万
@@ -32039,7 +32039,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2451万
@@ -32047,7 +32047,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2321万
@@ -32062,7 +32062,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $987万
@@ -32070,7 +32070,7 @@
 (25年-06月-30日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $969万
@@ -32078,7 +32078,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1034万
@@ -32086,7 +32086,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $934万
@@ -32094,7 +32094,7 @@
 (25年-06月-14日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $888万
@@ -32102,7 +32102,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2727万
@@ -32110,7 +32110,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2426万
@@ -32118,7 +32118,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2310万
@@ -32133,7 +32133,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $983万
@@ -32141,7 +32141,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $965万
@@ -32149,7 +32149,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $969万
@@ -32157,7 +32157,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $988万
@@ -32165,7 +32165,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $885万
@@ -32173,7 +32173,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2701万
@@ -32181,7 +32181,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2402万
@@ -32189,7 +32189,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2294万
@@ -32204,7 +32204,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $979万
@@ -32212,7 +32212,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $949万
@@ -32220,7 +32220,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $965万
@@ -32228,7 +32228,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $927万
@@ -32236,7 +32236,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $926万
@@ -32244,7 +32244,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2674万
@@ -32252,7 +32252,7 @@
 (25年-07月-16日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2498万
@@ -32260,7 +32260,7 @@
 (25年-07月-25日)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2277万
@@ -32275,7 +32275,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $976万
@@ -32283,7 +32283,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $957万
@@ -32291,7 +32291,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $962万
@@ -32299,7 +32299,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $981万
@@ -32307,7 +32307,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $878万
@@ -32315,7 +32315,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2787万
@@ -32323,7 +32323,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2555万
@@ -32331,7 +32331,7 @@
 (25年-07月-18日)</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2355万
@@ -32346,7 +32346,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1032万
@@ -32354,7 +32354,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1013万
@@ -32362,7 +32362,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1018万
@@ -32370,7 +32370,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $919万
@@ -32378,7 +32378,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $874万
@@ -32386,7 +32386,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2622万
@@ -32394,7 +32394,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2378万
@@ -32402,7 +32402,7 @@
 (25年-08月-04日)</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2244万
@@ -32417,7 +32417,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1028万
@@ -32425,7 +32425,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1009万
@@ -32433,7 +32433,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $1014万
@@ -32441,7 +32441,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $916万
@@ -32449,7 +32449,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -32457,7 +32457,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2734万
@@ -32465,7 +32465,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2382万
@@ -32473,7 +32473,7 @@
 (25年-08月-21日)</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2304万
@@ -32488,7 +32488,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1024万
@@ -32496,7 +32496,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $934万
@@ -32504,7 +32504,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $950万
@@ -32512,7 +32512,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $969万
@@ -32520,7 +32520,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -32528,7 +32528,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="G32" s="21" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2715万
@@ -32536,7 +32536,7 @@
 (25年-08月-01日)</t>
         </is>
       </c>
-      <c r="H32" s="21" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32544,7 +32544,7 @@
 (25年-08月-19日)</t>
         </is>
       </c>
-      <c r="I32" s="21" t="inlineStr">
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2211万
@@ -32559,7 +32559,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1020万
@@ -32567,7 +32567,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $1001万
@@ -32575,7 +32575,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $946万
@@ -32583,7 +32583,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $908万
@@ -32591,7 +32591,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $864万
@@ -32599,7 +32599,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2584万
@@ -32607,7 +32607,7 @@
 (25年-08月-11日)</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2348万
@@ -32615,7 +32615,7 @@
 (25年-08月-19日)</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2272万
@@ -32630,7 +32630,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $1016万
@@ -32638,7 +32638,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $938万
@@ -32646,7 +32646,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $943万
@@ -32654,7 +32654,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $905万
@@ -32662,7 +32662,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $914万
@@ -32670,7 +32670,7 @@
 (25年-07月-09日)</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2565万
@@ -32678,7 +32678,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="H34" s="21" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2331万
@@ -32686,7 +32686,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2296万
@@ -32701,7 +32701,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $952万
@@ -32709,7 +32709,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $993万
@@ -32717,7 +32717,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $939万
@@ -32725,7 +32725,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $901万
@@ -32733,7 +32733,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $911万
@@ -32741,7 +32741,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2680万
@@ -32749,7 +32749,7 @@
 (25年-09月-03日)</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2313万
@@ -32757,7 +32757,7 @@
 (25年-09月-26日)</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2280万
@@ -32772,7 +32772,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $949万
@@ -32780,7 +32780,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $931万
@@ -32788,7 +32788,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $935万
@@ -32796,7 +32796,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $954万
@@ -32804,7 +32804,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $854万
@@ -32812,7 +32812,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="G36" s="21" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2556万
@@ -32820,7 +32820,7 @@
 (25年-09月-12日)</t>
         </is>
       </c>
-      <c r="H36" s="21" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2339万
@@ -32828,7 +32828,7 @@
 (25年-10月-15日)</t>
         </is>
       </c>
-      <c r="I36" s="21" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2263万
@@ -32843,7 +32843,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>A | 486呎 (2房)
 $945万
@@ -32851,7 +32851,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>B | 485呎 (2房)
 $927万
@@ -32859,7 +32859,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 490呎 (2房)
 $931万
@@ -32867,7 +32867,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>D | 476呎 (2房)
 $894万
@@ -32875,7 +32875,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $850万
@@ -32883,7 +32883,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2574万
@@ -32891,7 +32891,7 @@
 (25年-10月-09日)</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2365万
@@ -32899,7 +32899,7 @@
 (25年-10月-21日)</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2247万
@@ -32914,7 +32914,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>A | 440呎 (2房)
 $1158万
@@ -32922,7 +32922,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>B | 439呎 (2房)
 $1089万
@@ -32930,7 +32930,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>C | 444呎 (2房)
 $1092万
@@ -32938,7 +32938,7 @@
 (25年-07月-11日)</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>D | 430呎 (2房)
 $1182万
@@ -32946,7 +32946,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $1040万
@@ -32954,7 +32954,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>P1 | 926呎 (3房)
 $2546万
@@ -32962,7 +32962,7 @@
 (25年-10月-10日)</t>
         </is>
       </c>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>P2 | 860呎 (3房)
 $2471万
@@ -32970,7 +32970,7 @@
 (25年-10月-22日)</t>
         </is>
       </c>
-      <c r="I38" s="21" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>P3 | 826呎 (3房)
 $2354万
